--- a/Team-Data/2010-11/3-21-2010-11.xlsx
+++ b/Team-Data/2010-11/3-21-2010-11.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J2" t="n">
         <v>78.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L2" t="n">
         <v>6.4</v>
       </c>
       <c r="M2" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O2" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
         <v>9.5</v>
       </c>
       <c r="S2" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T2" t="n">
         <v>39.7</v>
       </c>
       <c r="U2" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V2" t="n">
         <v>13.8</v>
@@ -730,16 +797,16 @@
         <v>18.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -763,13 +830,13 @@
         <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM2" t="n">
         <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -784,7 +851,7 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -799,10 +866,10 @@
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" t="n">
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.731</v>
+        <v>0.721</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J3" t="n">
-        <v>76.5</v>
+        <v>76.3</v>
       </c>
       <c r="K3" t="n">
         <v>0.488</v>
       </c>
       <c r="L3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="O3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P3" t="n">
         <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.764</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="S3" t="n">
         <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U3" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X3" t="n">
         <v>4.3</v>
@@ -915,13 +982,13 @@
         <v>20.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>97.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -930,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
         <v>22</v>
@@ -951,10 +1018,10 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
         <v>25</v>
@@ -969,13 +1036,13 @@
         <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -984,7 +1051,7 @@
         <v>22</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
@@ -996,7 +1063,7 @@
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.412</v>
+        <v>0.406</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J4" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
@@ -1064,22 +1131,22 @@
         <v>24.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T4" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U4" t="n">
         <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
         <v>6.4</v>
@@ -1091,25 +1158,25 @@
         <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>21</v>
@@ -1130,7 +1197,7 @@
         <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN4" t="n">
         <v>28</v>
@@ -1145,22 +1212,22 @@
         <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
         <v>8</v>
@@ -1172,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -1210,85 +1277,85 @@
         <v>68</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.735</v>
+        <v>0.721</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.362</v>
+        <v>0.355</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U5" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V5" t="n">
         <v>14.2</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>5.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
         <v>2</v>
@@ -1297,31 +1364,31 @@
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL5" t="n">
         <v>17</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>15</v>
       </c>
       <c r="AM5" t="n">
         <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>26</v>
@@ -1342,25 +1409,25 @@
         <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -1392,25 +1459,25 @@
         <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.176</v>
+        <v>0.191</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
         <v>81.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L6" t="n">
         <v>6.3</v>
@@ -1419,7 +1486,7 @@
         <v>18.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
         <v>18.7</v>
@@ -1455,19 +1522,19 @@
         <v>6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AC6" t="n">
-        <v>-10.8</v>
+        <v>-10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>30</v>
@@ -1500,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
@@ -1521,22 +1588,22 @@
         <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
         <v>29</v>
       </c>
       <c r="AY6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ6" t="n">
         <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
         <v>26</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O7" t="n">
         <v>17.6</v>
@@ -1628,7 +1695,7 @@
         <v>13.7</v>
       </c>
       <c r="W7" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
@@ -1643,16 +1710,16 @@
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
         <v>5</v>
@@ -1676,19 +1743,19 @@
         <v>8</v>
       </c>
       <c r="AM7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>5</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6</v>
       </c>
       <c r="AR7" t="n">
         <v>29</v>
@@ -1700,13 +1767,13 @@
         <v>16</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
         <v>24</v>
@@ -1718,13 +1785,13 @@
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -1768,10 +1835,10 @@
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.475</v>
@@ -1789,22 +1856,22 @@
         <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R8" t="n">
         <v>9.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T8" t="n">
         <v>41.7</v>
       </c>
       <c r="U8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V8" t="n">
         <v>14.1</v>
@@ -1813,25 +1880,25 @@
         <v>7.2</v>
       </c>
       <c r="X8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA8" t="n">
         <v>22.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.4</v>
+        <v>107.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,7 +1913,7 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>20</v>
@@ -1858,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
         <v>3</v>
@@ -1873,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
@@ -1885,19 +1952,19 @@
         <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.362</v>
+        <v>0.357</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1953,28 +2020,28 @@
         <v>36.9</v>
       </c>
       <c r="J9" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.454</v>
       </c>
       <c r="L9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O9" t="n">
         <v>16.4</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="R9" t="n">
         <v>11.3</v>
@@ -1983,13 +2050,13 @@
         <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="U9" t="n">
         <v>20.8</v>
       </c>
       <c r="V9" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
@@ -2004,16 +2071,16 @@
         <v>19.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2028,7 +2095,7 @@
         <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>14</v>
@@ -2037,19 +2104,19 @@
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
         <v>27</v>
@@ -2058,7 +2125,7 @@
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
         <v>30</v>
@@ -2076,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
         <v>7</v>
@@ -2085,7 +2152,7 @@
         <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -2120,43 +2187,43 @@
         <v>70</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.414</v>
+        <v>0.429</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.458</v>
+        <v>0.46</v>
       </c>
       <c r="L10" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="O10" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
@@ -2168,13 +2235,13 @@
         <v>40.1</v>
       </c>
       <c r="U10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X10" t="n">
         <v>4.8</v>
@@ -2183,46 +2250,46 @@
         <v>4.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>102.1</v>
+        <v>102.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
       <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM10" t="n">
         <v>5</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>6</v>
       </c>
       <c r="AN10" t="n">
         <v>2</v>
@@ -2234,22 +2301,22 @@
         <v>30</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
         <v>23</v>
       </c>
       <c r="AU10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
@@ -2258,10 +2325,10 @@
         <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" t="n">
         <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>0.536</v>
+        <v>0.521</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J11" t="n">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O11" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="P11" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.795</v>
+        <v>0.797</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S11" t="n">
         <v>30.9</v>
       </c>
       <c r="T11" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U11" t="n">
         <v>23.4</v>
@@ -2356,7 +2423,7 @@
         <v>13.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>4.7</v>
@@ -2365,31 +2432,31 @@
         <v>5.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.1</v>
+        <v>105.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
         <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2410,22 +2477,22 @@
         <v>12</v>
       </c>
       <c r="AO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" t="n">
         <v>5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
         <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
         <v>5</v>
@@ -2434,7 +2501,7 @@
         <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>17</v>
@@ -2446,7 +2513,7 @@
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -2484,52 +2551,52 @@
         <v>70</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>0.443</v>
+        <v>0.429</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J12" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>7.2</v>
       </c>
       <c r="M12" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O12" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P12" t="n">
         <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.788</v>
+        <v>0.784</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.8</v>
+        <v>32.6</v>
       </c>
       <c r="T12" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
@@ -2538,7 +2605,7 @@
         <v>15.4</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
         <v>5.7</v>
@@ -2547,19 +2614,19 @@
         <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.3</v>
+        <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2571,16 +2638,16 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
         <v>9</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>9</v>
@@ -2598,13 +2665,13 @@
         <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
@@ -2619,19 +2686,19 @@
         <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" t="n">
         <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>0.386</v>
+        <v>0.38</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L13" t="n">
         <v>6.4</v>
@@ -2693,7 +2760,7 @@
         <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
         <v>19.1</v>
@@ -2702,7 +2769,7 @@
         <v>26.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R13" t="n">
         <v>11.6</v>
@@ -2714,7 +2781,7 @@
         <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
         <v>16.1</v>
@@ -2729,16 +2796,16 @@
         <v>4.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
         <v>22.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -2753,25 +2820,25 @@
         <v>23</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
         <v>19</v>
       </c>
       <c r="AL13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM13" t="n">
         <v>11</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
@@ -2783,19 +2850,19 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
         <v>12</v>
       </c>
-      <c r="AU13" t="n">
-        <v>11</v>
-      </c>
       <c r="AV13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
@@ -2807,13 +2874,13 @@
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.71</v>
+        <v>0.714</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,22 +2930,22 @@
         <v>38.1</v>
       </c>
       <c r="J14" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L14" t="n">
         <v>6.4</v>
       </c>
       <c r="M14" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="O14" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P14" t="n">
         <v>23.7</v>
@@ -2896,37 +2963,37 @@
         <v>43.7</v>
       </c>
       <c r="U14" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V14" t="n">
         <v>13.1</v>
       </c>
       <c r="W14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA14" t="n">
         <v>20.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.1</v>
+        <v>101.3</v>
       </c>
       <c r="AC14" t="n">
         <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2938,22 +3005,22 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>13</v>
@@ -2965,7 +3032,7 @@
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>10</v>
@@ -2974,7 +3041,7 @@
         <v>4</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
         <v>2</v>
@@ -2986,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -3030,70 +3097,70 @@
         <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.543</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J15" t="n">
         <v>83.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L15" t="n">
         <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.327</v>
       </c>
       <c r="O15" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T15" t="n">
         <v>41</v>
       </c>
       <c r="U15" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="V15" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W15" t="n">
         <v>9.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
         <v>21.4</v>
@@ -3102,22 +3169,22 @@
         <v>100</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI15" t="n">
         <v>3</v>
@@ -3141,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3153,10 +3220,10 @@
         <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>13</v>
@@ -3171,16 +3238,16 @@
         <v>30</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>0.479</v>
+        <v>0.477</v>
       </c>
       <c r="L16" t="n">
         <v>6.6</v>
@@ -3239,7 +3306,7 @@
         <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O16" t="n">
         <v>21.4</v>
@@ -3248,28 +3315,28 @@
         <v>27.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R16" t="n">
         <v>9.5</v>
       </c>
       <c r="S16" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T16" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
         <v>2.9</v>
@@ -3281,28 +3348,28 @@
         <v>21.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>101.9</v>
+        <v>101.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3314,10 +3381,10 @@
         <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3335,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="AT16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
         <v>28</v>
@@ -3344,7 +3411,7 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
         <v>7</v>
@@ -3356,13 +3423,13 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>0.412</v>
+        <v>0.406</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="J17" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K17" t="n">
         <v>0.427</v>
@@ -3418,7 +3485,7 @@
         <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>0.343</v>
@@ -3427,25 +3494,25 @@
         <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.75</v>
+        <v>0.747</v>
       </c>
       <c r="R17" t="n">
         <v>10.9</v>
       </c>
       <c r="S17" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T17" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="V17" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W17" t="n">
         <v>7.5</v>
@@ -3457,10 +3524,10 @@
         <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB17" t="n">
         <v>91.5</v>
@@ -3469,13 +3536,13 @@
         <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
         <v>21</v>
@@ -3496,13 +3563,13 @@
         <v>20</v>
       </c>
       <c r="AM17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN17" t="n">
         <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3511,10 +3578,10 @@
         <v>23</v>
       </c>
       <c r="AR17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
@@ -3526,10 +3593,10 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J18" t="n">
         <v>85.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
@@ -3603,25 +3670,25 @@
         <v>19.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O18" t="n">
         <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.767</v>
       </c>
       <c r="R18" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="S18" t="n">
         <v>31.4</v>
       </c>
       <c r="T18" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U18" t="n">
         <v>20.3</v>
@@ -3633,19 +3700,19 @@
         <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y18" t="n">
         <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA18" t="n">
         <v>21.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>101.2</v>
+        <v>101.4</v>
       </c>
       <c r="AC18" t="n">
         <v>-5.8</v>
@@ -3660,13 +3727,13 @@
         <v>29</v>
       </c>
       <c r="AG18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH18" t="n">
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3675,13 +3742,13 @@
         <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM18" t="n">
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
         <v>9</v>
@@ -3720,13 +3787,13 @@
         <v>29</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
         <v>9</v>
       </c>
       <c r="BC18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -3758,13 +3825,13 @@
         <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>0.309</v>
+        <v>0.324</v>
       </c>
       <c r="H19" t="n">
         <v>48.9</v>
@@ -3773,67 +3840,67 @@
         <v>35.1</v>
       </c>
       <c r="J19" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P19" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0.759</v>
       </c>
       <c r="R19" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T19" t="n">
         <v>41.5</v>
       </c>
       <c r="U19" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V19" t="n">
         <v>14.4</v>
       </c>
       <c r="W19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z19" t="n">
         <v>22.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3851,10 +3918,10 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>21</v>
@@ -3863,10 +3930,10 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP19" t="n">
         <v>21</v>
@@ -3875,10 +3942,10 @@
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
         <v>14</v>
@@ -3887,7 +3954,7 @@
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
@@ -3896,19 +3963,19 @@
         <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F20" t="n">
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3958,22 +4025,22 @@
         <v>78</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0.767</v>
@@ -3982,31 +4049,31 @@
         <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T20" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U20" t="n">
         <v>20.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB20" t="n">
         <v>94.7</v>
@@ -4027,7 +4094,7 @@
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4045,13 +4112,13 @@
         <v>25</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
         <v>14</v>
@@ -4063,16 +4130,16 @@
         <v>14</v>
       </c>
       <c r="AT20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU20" t="n">
         <v>20</v>
       </c>
-      <c r="AU20" t="n">
-        <v>22</v>
-      </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
@@ -4084,13 +4151,13 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB20" t="n">
         <v>27</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -4122,22 +4189,22 @@
         <v>69</v>
       </c>
       <c r="E21" t="n">
+        <v>35</v>
+      </c>
+      <c r="F21" t="n">
         <v>34</v>
       </c>
-      <c r="F21" t="n">
-        <v>35</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.493</v>
+        <v>0.507</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J21" t="n">
-        <v>83.5</v>
+        <v>83.7</v>
       </c>
       <c r="K21" t="n">
         <v>0.46</v>
@@ -4146,31 +4213,31 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O21" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R21" t="n">
         <v>10.3</v>
       </c>
       <c r="S21" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
         <v>14.1</v>
@@ -4179,10 +4246,10 @@
         <v>7.6</v>
       </c>
       <c r="X21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z21" t="n">
         <v>21.2</v>
@@ -4191,19 +4258,19 @@
         <v>20.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>17</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
         <v>18</v>
@@ -4215,10 +4282,10 @@
         <v>5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
         <v>2</v>
@@ -4227,10 +4294,10 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP21" t="n">
         <v>9</v>
@@ -4245,7 +4312,7 @@
         <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>15</v>
@@ -4257,16 +4324,16 @@
         <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -4301,52 +4368,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.647</v>
+        <v>0.652</v>
       </c>
       <c r="H22" t="n">
         <v>48.8</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J22" t="n">
         <v>80.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M22" t="n">
         <v>17</v>
       </c>
       <c r="N22" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="P22" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.825</v>
+        <v>0.824</v>
       </c>
       <c r="R22" t="n">
         <v>10.8</v>
       </c>
       <c r="S22" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T22" t="n">
         <v>42.5</v>
@@ -4361,25 +4428,25 @@
         <v>7.9</v>
       </c>
       <c r="X22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y22" t="n">
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB22" t="n">
         <v>104.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -4397,19 +4464,19 @@
         <v>16</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4439,16 +4506,16 @@
         <v>5</v>
       </c>
       <c r="AX22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY22" t="n">
         <v>6</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AZ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA22" t="n">
         <v>5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -4498,43 +4565,43 @@
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L23" t="n">
         <v>9.4</v>
       </c>
       <c r="M23" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O23" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
         <v>14.8</v>
@@ -4546,25 +4613,25 @@
         <v>4.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
         <v>8</v>
@@ -4573,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
@@ -4582,7 +4649,7 @@
         <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,13 +4658,13 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,7 +4673,7 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -4618,10 +4685,10 @@
         <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY23" t="n">
         <v>3</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
         <v>36</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>0.522</v>
+        <v>0.514</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
@@ -4692,34 +4759,34 @@
         <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P24" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R24" t="n">
         <v>10.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T24" t="n">
         <v>42.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V24" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W24" t="n">
         <v>7.6</v>
@@ -4731,34 +4798,34 @@
         <v>4.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG24" t="n">
         <v>16</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
         <v>11</v>
@@ -4770,16 +4837,16 @@
         <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
@@ -4788,16 +4855,16 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW24" t="n">
         <v>9</v>
@@ -4806,7 +4873,7 @@
         <v>25</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4815,10 +4882,10 @@
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -4847,13 +4914,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
         <v>0.515</v>
@@ -4862,10 +4929,10 @@
         <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J25" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.47</v>
@@ -4874,34 +4941,34 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
         <v>23.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
       </c>
       <c r="S25" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T25" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U25" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V25" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W25" t="n">
         <v>6.6</v>
@@ -4913,19 +4980,19 @@
         <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="AC25" t="n">
         <v>-0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -4934,13 +5001,13 @@
         <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>3</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
         <v>8</v>
@@ -4955,7 +5022,7 @@
         <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
         <v>15</v>
@@ -4970,31 +5037,31 @@
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F26" t="n">
         <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.446</v>
@@ -5056,106 +5123,106 @@
         <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.344</v>
+        <v>0.347</v>
       </c>
       <c r="O26" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="R26" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S26" t="n">
         <v>27</v>
       </c>
       <c r="T26" t="n">
-        <v>39</v>
+        <v>39.3</v>
       </c>
       <c r="U26" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X26" t="n">
         <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA26" t="n">
         <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
         <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
         <v>24</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU26" t="n">
         <v>16</v>
@@ -5179,7 +5246,7 @@
         <v>16</v>
       </c>
       <c r="BB26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -5214,25 +5281,25 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G27" t="n">
-        <v>0.235</v>
+        <v>0.25</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J27" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>5.2</v>
@@ -5241,70 +5308,70 @@
         <v>15.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O27" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R27" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S27" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T27" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W27" t="n">
         <v>7.3</v>
       </c>
       <c r="X27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6</v>
+        <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="n">
         <v>3</v>
@@ -5319,10 +5386,10 @@
         <v>23</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
         <v>16</v>
@@ -5334,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT27" t="n">
         <v>5</v>
@@ -5343,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
         <v>21</v>
@@ -5358,13 +5425,13 @@
         <v>26</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -5420,28 +5487,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="O28" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P28" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q28" t="n">
         <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T28" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U28" t="n">
         <v>22.7</v>
@@ -5450,28 +5517,28 @@
         <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
         <v>4.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC28" t="n">
         <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,25 +5556,25 @@
         <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ28" t="n">
         <v>13</v>
@@ -5516,10 +5583,10 @@
         <v>23</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5528,10 +5595,10 @@
         <v>8</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
@@ -5546,7 +5613,7 @@
         <v>6</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -5590,28 +5657,28 @@
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L29" t="n">
         <v>4.3</v>
       </c>
       <c r="M29" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.315</v>
+        <v>0.314</v>
       </c>
       <c r="O29" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P29" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q29" t="n">
         <v>0.756</v>
@@ -5623,16 +5690,16 @@
         <v>28.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
         <v>22.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W29" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
@@ -5641,7 +5708,7 @@
         <v>5.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
         <v>20</v>
@@ -5650,10 +5717,10 @@
         <v>99.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-5.9</v>
+        <v>-5.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI29" t="n">
         <v>4</v>
@@ -5674,7 +5741,7 @@
         <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="n">
         <v>29</v>
@@ -5692,25 +5759,25 @@
         <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX29" t="n">
         <v>23</v>
@@ -5719,16 +5786,16 @@
         <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB29" t="n">
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
         <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.522</v>
+        <v>0.514</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
@@ -5787,25 +5854,25 @@
         <v>15.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O30" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R30" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T30" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="U30" t="n">
         <v>23.8</v>
@@ -5814,49 +5881,49 @@
         <v>14.1</v>
       </c>
       <c r="W30" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X30" t="n">
         <v>5.9</v>
       </c>
       <c r="Y30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD30" t="n">
         <v>5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
       </c>
       <c r="AF30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG30" t="n">
         <v>16</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>9</v>
       </c>
       <c r="AI30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
         <v>17</v>
       </c>
       <c r="AK30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,31 +5932,31 @@
         <v>22</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
         <v>8</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT30" t="n">
         <v>27</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
@@ -5939,55 +6006,55 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E31" t="n">
         <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
-        <v>0.254</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J31" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.334</v>
+        <v>0.332</v>
       </c>
       <c r="O31" t="n">
         <v>17.6</v>
       </c>
       <c r="P31" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T31" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U31" t="n">
         <v>19.8</v>
@@ -6011,13 +6078,13 @@
         <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.4</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
@@ -6032,10 +6099,10 @@
         <v>7</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
@@ -6050,7 +6117,7 @@
         <v>27</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
@@ -6065,7 +6132,7 @@
         <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-21-2010-11</t>
+          <t>2011-03-21</t>
         </is>
       </c>
     </row>
